--- a/Datos/Presupuesto de Egresos Municipales de Campeche.xlsx
+++ b/Datos/Presupuesto de Egresos Municipales de Campeche.xlsx
@@ -1,18 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Laboratorio de Ambientes Inteligentes\Proyecto Inundaciones\Proyecto_Recomendaciones_Inundaciones\Datos\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F37767-FE35-458F-B881-A457B7EE9B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Table 1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Referencias de fuentes" sheetId="2" r:id="rId6"/>
+    <sheet name="Table 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Referencias de fuentes" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="1042">
   <si>
     <t>Municipio</t>
   </si>
@@ -1878,20 +1887,1281 @@
   </si>
   <si>
     <t>PPTO_Eg_Tenabo_2023.pdf</t>
+  </si>
+  <si>
+    <t>Campeche</t>
+  </si>
+  <si>
+    <t>1864891792</t>
+  </si>
+  <si>
+    <t>648615359</t>
+  </si>
+  <si>
+    <t>211933688</t>
+  </si>
+  <si>
+    <t>441892513</t>
+  </si>
+  <si>
+    <t>487071157</t>
+  </si>
+  <si>
+    <t>1711229</t>
+  </si>
+  <si>
+    <t>72344445</t>
+  </si>
+  <si>
+    <t>133766939</t>
+  </si>
+  <si>
+    <t>285743658</t>
+  </si>
+  <si>
+    <t>831208317</t>
+  </si>
+  <si>
+    <t>87281022</t>
+  </si>
+  <si>
+    <t>89008728</t>
+  </si>
+  <si>
+    <t>525378480</t>
+  </si>
+  <si>
+    <t>96901051</t>
+  </si>
+  <si>
+    <t>34553547</t>
+  </si>
+  <si>
+    <t>773172840</t>
+  </si>
+  <si>
+    <t>231156514</t>
+  </si>
+  <si>
+    <t>97151051</t>
+  </si>
+  <si>
+    <t>La Dirección de Servicios Públicos concentra el mayor monto operativo. El presupuesto para seguridad pública es absorbido por el Estado. Incluye fe de erratas con Anexo XX de igualdad de género y datos del SMAPAC.</t>
+  </si>
+  <si>
+    <t>1802345813</t>
+  </si>
+  <si>
+    <t>635897411</t>
+  </si>
+  <si>
+    <t>205490576</t>
+  </si>
+  <si>
+    <t>385036396</t>
+  </si>
+  <si>
+    <t>482957092</t>
+  </si>
+  <si>
+    <t>719420</t>
+  </si>
+  <si>
+    <t>75143345</t>
+  </si>
+  <si>
+    <t>15759573</t>
+  </si>
+  <si>
+    <t>130143345</t>
+  </si>
+  <si>
+    <t>267799118</t>
+  </si>
+  <si>
+    <t>772459810</t>
+  </si>
+  <si>
+    <t>11982344</t>
+  </si>
+  <si>
+    <t>87040949</t>
+  </si>
+  <si>
+    <t>307434116</t>
+  </si>
+  <si>
+    <t>674305427</t>
+  </si>
+  <si>
+    <t>4029193</t>
+  </si>
+  <si>
+    <t>68643039</t>
+  </si>
+  <si>
+    <t>28972081</t>
+  </si>
+  <si>
+    <t>799519506</t>
+  </si>
+  <si>
+    <t>210598651</t>
+  </si>
+  <si>
+    <t>La Seguridad Pública no es administrada por el H. Ayuntamiento; el gasto lo absorbe el Estado. Presupuesto en equilibrio con la Ley de Ingresos.</t>
+  </si>
+  <si>
+    <t>1877173589</t>
+  </si>
+  <si>
+    <t>118856150</t>
+  </si>
+  <si>
+    <t>409922393</t>
+  </si>
+  <si>
+    <t>536735500</t>
+  </si>
+  <si>
+    <t>14013063</t>
+  </si>
+  <si>
+    <t>64884453</t>
+  </si>
+  <si>
+    <t>95522618</t>
+  </si>
+  <si>
+    <t>122509951</t>
+  </si>
+  <si>
+    <t>262685443</t>
+  </si>
+  <si>
+    <t>752000096</t>
+  </si>
+  <si>
+    <t>16999921</t>
+  </si>
+  <si>
+    <t>77325653</t>
+  </si>
+  <si>
+    <t>362770437</t>
+  </si>
+  <si>
+    <t>551270225</t>
+  </si>
+  <si>
+    <t>3657378</t>
+  </si>
+  <si>
+    <t>70484149</t>
+  </si>
+  <si>
+    <t>26314983</t>
+  </si>
+  <si>
+    <t>860493984</t>
+  </si>
+  <si>
+    <t>191026681</t>
+  </si>
+  <si>
+    <t>54744841</t>
+  </si>
+  <si>
+    <t>La Seguridad Pública no es administrada por el H. Ayuntamiento; el gasto lo absorbe el Estado. Incluye transferencias a organismos descentralizados (SMAPAC, DIF).</t>
+  </si>
+  <si>
+    <t>1545138951</t>
+  </si>
+  <si>
+    <t>628633872</t>
+  </si>
+  <si>
+    <t>98955023</t>
+  </si>
+  <si>
+    <t>245156736</t>
+  </si>
+  <si>
+    <t>389434494</t>
+  </si>
+  <si>
+    <t>15506157</t>
+  </si>
+  <si>
+    <t>82478447</t>
+  </si>
+  <si>
+    <t>83632223</t>
+  </si>
+  <si>
+    <t>85556692</t>
+  </si>
+  <si>
+    <t>220282161</t>
+  </si>
+  <si>
+    <t>685192748</t>
+  </si>
+  <si>
+    <t>13584531</t>
+  </si>
+  <si>
+    <t>57846110</t>
+  </si>
+  <si>
+    <t>262945416</t>
+  </si>
+  <si>
+    <t>493636121</t>
+  </si>
+  <si>
+    <t>5560767</t>
+  </si>
+  <si>
+    <t>34133058</t>
+  </si>
+  <si>
+    <t>25314983</t>
+  </si>
+  <si>
+    <t>738212999</t>
+  </si>
+  <si>
+    <t>137598200</t>
+  </si>
+  <si>
+    <t>La Seguridad Pública no es administrada por el municipio. Se reportan transferencias a 4 Juntas Municipales, 8 Comisarías y 27 Agencias Municipales.</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>2032535696</t>
+  </si>
+  <si>
+    <t>740000000</t>
+  </si>
+  <si>
+    <t>124537268</t>
+  </si>
+  <si>
+    <t>446103011</t>
+  </si>
+  <si>
+    <t>196322156</t>
+  </si>
+  <si>
+    <t>34247957</t>
+  </si>
+  <si>
+    <t>448485334</t>
+  </si>
+  <si>
+    <t>42839968</t>
+  </si>
+  <si>
+    <t>195640280</t>
+  </si>
+  <si>
+    <t>241793410</t>
+  </si>
+  <si>
+    <t>835709672</t>
+  </si>
+  <si>
+    <t>29121935</t>
+  </si>
+  <si>
+    <t>524431805</t>
+  </si>
+  <si>
+    <t>136396444</t>
+  </si>
+  <si>
+    <t>241879562</t>
+  </si>
+  <si>
+    <t>126362771</t>
+  </si>
+  <si>
+    <t>7200000000</t>
+  </si>
+  <si>
+    <t>El Agua Potable (SMAPAC) es ejercido directamente. Se reportan 2530 plazas en la administración centralizada.</t>
+  </si>
+  <si>
+    <t>730000000</t>
+  </si>
+  <si>
+    <t>110482210</t>
+  </si>
+  <si>
+    <t>317510741</t>
+  </si>
+  <si>
+    <t>333070713</t>
+  </si>
+  <si>
+    <t>28730442</t>
+  </si>
+  <si>
+    <t>455357231</t>
+  </si>
+  <si>
+    <t>57384358</t>
+  </si>
+  <si>
+    <t>24263911</t>
+  </si>
+  <si>
+    <t>457452821</t>
+  </si>
+  <si>
+    <t>147146444</t>
+  </si>
+  <si>
+    <t>314183089</t>
+  </si>
+  <si>
+    <t>2673624</t>
+  </si>
+  <si>
+    <t>75264513</t>
+  </si>
+  <si>
+    <t>72000000</t>
+  </si>
+  <si>
+    <t>14400000</t>
+  </si>
+  <si>
+    <t>Incluye transferencias a IMUVI, IMM e INDEJUCAR. Cap 9000 incluye ADEFAS. Fe de erratas sobre transferencias a DIF, IMUVI, SMAPAC y autoridades auxiliares.</t>
+  </si>
+  <si>
+    <t>5, 6, 7</t>
+  </si>
+  <si>
+    <t>1882914635</t>
+  </si>
+  <si>
+    <t>159516329</t>
+  </si>
+  <si>
+    <t>343122341</t>
+  </si>
+  <si>
+    <t>35801752</t>
+  </si>
+  <si>
+    <t>331572317</t>
+  </si>
+  <si>
+    <t>40524985</t>
+  </si>
+  <si>
+    <t>190855088</t>
+  </si>
+  <si>
+    <t>226608921</t>
+  </si>
+  <si>
+    <t>780757734</t>
+  </si>
+  <si>
+    <t>46935182</t>
+  </si>
+  <si>
+    <t>73513067</t>
+  </si>
+  <si>
+    <t>140970466</t>
+  </si>
+  <si>
+    <t>258480016</t>
+  </si>
+  <si>
+    <t>16178851</t>
+  </si>
+  <si>
+    <t>52100400</t>
+  </si>
+  <si>
+    <t>Discrepancia entre Artículo 7 ( $1,878,914,635$ ) y sumatoria de capítulos ( $1,882,914,635$ ). Fe de erratas ajusta materiales, transferencias y deuda pública.</t>
+  </si>
+  <si>
+    <t>8, 9</t>
+  </si>
+  <si>
+    <t>1873146791</t>
+  </si>
+  <si>
+    <t>708380946</t>
+  </si>
+  <si>
+    <t>114318912</t>
+  </si>
+  <si>
+    <t>263164419</t>
+  </si>
+  <si>
+    <t>348351682</t>
+  </si>
+  <si>
+    <t>30834212</t>
+  </si>
+  <si>
+    <t>349271742</t>
+  </si>
+  <si>
+    <t>58824875</t>
+  </si>
+  <si>
+    <t>181693761</t>
+  </si>
+  <si>
+    <t>222281780</t>
+  </si>
+  <si>
+    <t>786180410</t>
+  </si>
+  <si>
+    <t>45019119</t>
+  </si>
+  <si>
+    <t>421711204</t>
+  </si>
+  <si>
+    <t>136077419</t>
+  </si>
+  <si>
+    <t>348095003</t>
+  </si>
+  <si>
+    <t>61413381</t>
+  </si>
+  <si>
+    <t>60000000</t>
+  </si>
+  <si>
+    <t>El presupuesto para SMAPAC es ejercido directamente. La administración centralizada cuenta con 2133 plazas.</t>
+  </si>
+  <si>
+    <t>1645479378</t>
+  </si>
+  <si>
+    <t>712174175</t>
+  </si>
+  <si>
+    <t>76361483</t>
+  </si>
+  <si>
+    <t>313330840</t>
+  </si>
+  <si>
+    <t>322058488</t>
+  </si>
+  <si>
+    <t>14809311</t>
+  </si>
+  <si>
+    <t>166723752</t>
+  </si>
+  <si>
+    <t>40021329</t>
+  </si>
+  <si>
+    <t>126256668</t>
+  </si>
+  <si>
+    <t>186400549</t>
+  </si>
+  <si>
+    <t>740695093</t>
+  </si>
+  <si>
+    <t>44231344</t>
+  </si>
+  <si>
+    <t>110911791</t>
+  </si>
+  <si>
+    <t>132933885</t>
+  </si>
+  <si>
+    <t>328726845</t>
+  </si>
+  <si>
+    <t>70804287</t>
+  </si>
+  <si>
+    <t>1073203271</t>
+  </si>
+  <si>
+    <t>7702336</t>
+  </si>
+  <si>
+    <t>Modificación por sentencia del Tribunal Electoral. Incluye transferencias a SMAPAC, INDEJUCAR y entidades paramunicipales ( $82,600,000$ ).</t>
+  </si>
+  <si>
+    <t>11, 12</t>
+  </si>
+  <si>
+    <t>Candelaria</t>
+  </si>
+  <si>
+    <t>469999160</t>
+  </si>
+  <si>
+    <t>132968480</t>
+  </si>
+  <si>
+    <t>25193474</t>
+  </si>
+  <si>
+    <t>51757645</t>
+  </si>
+  <si>
+    <t>31201182</t>
+  </si>
+  <si>
+    <t>14520512</t>
+  </si>
+  <si>
+    <t>170546839</t>
+  </si>
+  <si>
+    <t>43451028</t>
+  </si>
+  <si>
+    <t>194198477</t>
+  </si>
+  <si>
+    <t>49085767</t>
+  </si>
+  <si>
+    <t>153159721</t>
+  </si>
+  <si>
+    <t>8027482</t>
+  </si>
+  <si>
+    <t>215464758</t>
+  </si>
+  <si>
+    <t>10459482</t>
+  </si>
+  <si>
+    <t>30581760</t>
+  </si>
+  <si>
+    <t>9730482</t>
+  </si>
+  <si>
+    <t>12300000</t>
+  </si>
+  <si>
+    <t>228987708</t>
+  </si>
+  <si>
+    <t>27395482</t>
+  </si>
+  <si>
+    <t>La Unidad de Presidencia incluye transferencias al DIF. No se contemplan recursos para justicia municipal.</t>
+  </si>
+  <si>
+    <t>431559527</t>
+  </si>
+  <si>
+    <t>125796068</t>
+  </si>
+  <si>
+    <t>18079156</t>
+  </si>
+  <si>
+    <t>49202328</t>
+  </si>
+  <si>
+    <t>32016692</t>
+  </si>
+  <si>
+    <t>14654759</t>
+  </si>
+  <si>
+    <t>187210524</t>
+  </si>
+  <si>
+    <t>4500000</t>
+  </si>
+  <si>
+    <t>183189930</t>
+  </si>
+  <si>
+    <t>45583613</t>
+  </si>
+  <si>
+    <t>152546039</t>
+  </si>
+  <si>
+    <t>7148608</t>
+  </si>
+  <si>
+    <t>164546809</t>
+  </si>
+  <si>
+    <t>10267849</t>
+  </si>
+  <si>
+    <t>41037689</t>
+  </si>
+  <si>
+    <t>11300000</t>
+  </si>
+  <si>
+    <t>226546060</t>
+  </si>
+  <si>
+    <t>20592834</t>
+  </si>
+  <si>
+    <t>La Unidad de Presidencia incluye transferencias al DIF. Incluye asignaciones para Juntas Municipales (Monclova y Miguel Hidalgo).</t>
+  </si>
+  <si>
+    <t>420900271</t>
+  </si>
+  <si>
+    <t>124952382</t>
+  </si>
+  <si>
+    <t>20626897</t>
+  </si>
+  <si>
+    <t>48042855</t>
+  </si>
+  <si>
+    <t>34051380</t>
+  </si>
+  <si>
+    <t>5383716</t>
+  </si>
+  <si>
+    <t>187173041</t>
+  </si>
+  <si>
+    <t>179928285</t>
+  </si>
+  <si>
+    <t>42720988</t>
+  </si>
+  <si>
+    <t>151593028</t>
+  </si>
+  <si>
+    <t>6696390</t>
+  </si>
+  <si>
+    <t>13247808</t>
+  </si>
+  <si>
+    <t>9987544</t>
+  </si>
+  <si>
+    <t>45753142</t>
+  </si>
+  <si>
+    <t>7593995</t>
+  </si>
+  <si>
+    <t>10800000</t>
+  </si>
+  <si>
+    <t>272461857</t>
+  </si>
+  <si>
+    <t>20253400</t>
+  </si>
+  <si>
+    <t>Presupuesto coincide con Ley de Ingresos. Transferencias al DIF bajo Unidad de Presidencia. Sin justicia municipal.</t>
+  </si>
+  <si>
+    <t>415395755</t>
+  </si>
+  <si>
+    <t>123422218</t>
+  </si>
+  <si>
+    <t>21011891</t>
+  </si>
+  <si>
+    <t>48219117</t>
+  </si>
+  <si>
+    <t>32484443</t>
+  </si>
+  <si>
+    <t>14496673</t>
+  </si>
+  <si>
+    <t>174091413</t>
+  </si>
+  <si>
+    <t>176095592</t>
+  </si>
+  <si>
+    <t>41905223</t>
+  </si>
+  <si>
+    <t>154699447</t>
+  </si>
+  <si>
+    <t>7007576</t>
+  </si>
+  <si>
+    <t>14762759</t>
+  </si>
+  <si>
+    <t>12067092</t>
+  </si>
+  <si>
+    <t>52929802</t>
+  </si>
+  <si>
+    <t>10078679</t>
+  </si>
+  <si>
+    <t>8384363</t>
+  </si>
+  <si>
+    <t>272078366</t>
+  </si>
+  <si>
+    <t>12983715</t>
+  </si>
+  <si>
+    <t>Incluye transferencias al DIF. Se registran 50 expedientes laborales en trámite como deuda contingente.</t>
+  </si>
+  <si>
+    <t>557159195</t>
+  </si>
+  <si>
+    <t>120193596</t>
+  </si>
+  <si>
+    <t>18499126</t>
+  </si>
+  <si>
+    <t>40077215</t>
+  </si>
+  <si>
+    <t>24783000</t>
+  </si>
+  <si>
+    <t>15482158</t>
+  </si>
+  <si>
+    <t>335720546</t>
+  </si>
+  <si>
+    <t>122324284</t>
+  </si>
+  <si>
+    <t>35140786</t>
+  </si>
+  <si>
+    <t>142066590</t>
+  </si>
+  <si>
+    <t>5322614</t>
+  </si>
+  <si>
+    <t>360970486</t>
+  </si>
+  <si>
+    <t>10063159</t>
+  </si>
+  <si>
+    <t>54584574</t>
+  </si>
+  <si>
+    <t>439459315</t>
+  </si>
+  <si>
+    <t>10527486</t>
+  </si>
+  <si>
+    <t>La Unidad de Presidencia incluye transferencias al DIF. Incluye estudio actuarial de pensiones y expedientes laborales.</t>
+  </si>
+  <si>
+    <t>Calkiní</t>
+  </si>
+  <si>
+    <t>318275465</t>
+  </si>
+  <si>
+    <t>124948355</t>
+  </si>
+  <si>
+    <t>10207168</t>
+  </si>
+  <si>
+    <t>44989023</t>
+  </si>
+  <si>
+    <t>30570620</t>
+  </si>
+  <si>
+    <t>5923560</t>
+  </si>
+  <si>
+    <t>95106738</t>
+  </si>
+  <si>
+    <t>6530000</t>
+  </si>
+  <si>
+    <t>94517322</t>
+  </si>
+  <si>
+    <t>44868072</t>
+  </si>
+  <si>
+    <t>123498016</t>
+  </si>
+  <si>
+    <t>2333821</t>
+  </si>
+  <si>
+    <t>64489974</t>
+  </si>
+  <si>
+    <t>6470117</t>
+  </si>
+  <si>
+    <t>16422258</t>
+  </si>
+  <si>
+    <t>27495644</t>
+  </si>
+  <si>
+    <t>6696196</t>
+  </si>
+  <si>
+    <t>18283307</t>
+  </si>
+  <si>
+    <t>10000000</t>
+  </si>
+  <si>
+    <t>1150000</t>
+  </si>
+  <si>
+    <t>DIF Municipal incluido por clasificación. Se mencionan pasivos por demandas laborales y laudos pendientes.</t>
+  </si>
+  <si>
+    <t>300867371</t>
+  </si>
+  <si>
+    <t>113961331</t>
+  </si>
+  <si>
+    <t>12898017</t>
+  </si>
+  <si>
+    <t>51288767</t>
+  </si>
+  <si>
+    <t>25891080</t>
+  </si>
+  <si>
+    <t>3402000</t>
+  </si>
+  <si>
+    <t>93433177</t>
+  </si>
+  <si>
+    <t>88628313</t>
+  </si>
+  <si>
+    <t>41666841</t>
+  </si>
+  <si>
+    <t>121313999</t>
+  </si>
+  <si>
+    <t>2220954</t>
+  </si>
+  <si>
+    <t>64635711</t>
+  </si>
+  <si>
+    <t>6693145</t>
+  </si>
+  <si>
+    <t>46698130</t>
+  </si>
+  <si>
+    <t>21179460</t>
+  </si>
+  <si>
+    <t>Reporta 1063 plazas y 120 pensionados. El SM DIF se incluye por requerimiento de clasificación.</t>
+  </si>
+  <si>
+    <t>291376027</t>
+  </si>
+  <si>
+    <t>98173715</t>
+  </si>
+  <si>
+    <t>15194355</t>
+  </si>
+  <si>
+    <t>52433315</t>
+  </si>
+  <si>
+    <t>21994222</t>
+  </si>
+  <si>
+    <t>5577187</t>
+  </si>
+  <si>
+    <t>93003230</t>
+  </si>
+  <si>
+    <t>5000000</t>
+  </si>
+  <si>
+    <t>86533659</t>
+  </si>
+  <si>
+    <t>39050187</t>
+  </si>
+  <si>
+    <t>116851130</t>
+  </si>
+  <si>
+    <t>1982344</t>
+  </si>
+  <si>
+    <t>60527618</t>
+  </si>
+  <si>
+    <t>6908407</t>
+  </si>
+  <si>
+    <t>41634258</t>
+  </si>
+  <si>
+    <t>19498123</t>
+  </si>
+  <si>
+    <t>Desarrollo Social incluye funciones rural y económica. Provisión de  $5,000,000$  para ADEFAS.</t>
+  </si>
+  <si>
+    <t>291066910</t>
+  </si>
+  <si>
+    <t>102249534</t>
+  </si>
+  <si>
+    <t>17570805</t>
+  </si>
+  <si>
+    <t>52187526</t>
+  </si>
+  <si>
+    <t>19849580</t>
+  </si>
+  <si>
+    <t>2528298</t>
+  </si>
+  <si>
+    <t>86411167</t>
+  </si>
+  <si>
+    <t>82668069</t>
+  </si>
+  <si>
+    <t>38304516</t>
+  </si>
+  <si>
+    <t>117999073</t>
+  </si>
+  <si>
+    <t>1539111</t>
+  </si>
+  <si>
+    <t>56406466</t>
+  </si>
+  <si>
+    <t>6348793</t>
+  </si>
+  <si>
+    <t>47778184</t>
+  </si>
+  <si>
+    <t>38074074</t>
+  </si>
+  <si>
+    <t>19740557</t>
+  </si>
+  <si>
+    <t>6000000</t>
+  </si>
+  <si>
+    <t>582709</t>
+  </si>
+  <si>
+    <t>Pasivos laborales significativos por demandas ( $19,341,339$  total Ayto y DIF). Incluye juntas municipales y comisarías.</t>
+  </si>
+  <si>
+    <t>239297617</t>
+  </si>
+  <si>
+    <t>79455450</t>
+  </si>
+  <si>
+    <t>18978674</t>
+  </si>
+  <si>
+    <t>48610096</t>
+  </si>
+  <si>
+    <t>25206765</t>
+  </si>
+  <si>
+    <t>1147766</t>
+  </si>
+  <si>
+    <t>61898866</t>
+  </si>
+  <si>
+    <t>59719629</t>
+  </si>
+  <si>
+    <t>32121314</t>
+  </si>
+  <si>
+    <t>107787380</t>
+  </si>
+  <si>
+    <t>1639664</t>
+  </si>
+  <si>
+    <t>4966659</t>
+  </si>
+  <si>
+    <t>4930126</t>
+  </si>
+  <si>
+    <t>17519717</t>
+  </si>
+  <si>
+    <t>5393597</t>
+  </si>
+  <si>
+    <t>9792850</t>
+  </si>
+  <si>
+    <t>5851371</t>
+  </si>
+  <si>
+    <t>800330</t>
+  </si>
+  <si>
+    <t>Reporta 880 plazas laborales. Fe de erratas al tabulador de sueldos de personal de confianza.</t>
+  </si>
+  <si>
+    <t>22, 23</t>
+  </si>
+  <si>
+    <t>Calakmul</t>
+  </si>
+  <si>
+    <t>304891105</t>
+  </si>
+  <si>
+    <t>108297077</t>
+  </si>
+  <si>
+    <t>12721221</t>
+  </si>
+  <si>
+    <t>28642243</t>
+  </si>
+  <si>
+    <t>18929413</t>
+  </si>
+  <si>
+    <t>2710000</t>
+  </si>
+  <si>
+    <t>108179243</t>
+  </si>
+  <si>
+    <t>25411908</t>
+  </si>
+  <si>
+    <t>131806488</t>
+  </si>
+  <si>
+    <t>28880127</t>
+  </si>
+  <si>
+    <t>115499291</t>
+  </si>
+  <si>
+    <t>3492296</t>
+  </si>
+  <si>
+    <t>142456868</t>
+  </si>
+  <si>
+    <t>15344309</t>
+  </si>
+  <si>
+    <t>5589713</t>
+  </si>
+  <si>
+    <t>6995819</t>
+  </si>
+  <si>
+    <t>6177358</t>
+  </si>
+  <si>
+    <t>284663</t>
+  </si>
+  <si>
+    <t>101314580</t>
+  </si>
+  <si>
+    <t>Equilibrio con Ley de Ingresos. No se contemplan juzgados municipales.</t>
+  </si>
+  <si>
+    <t>292471382</t>
+  </si>
+  <si>
+    <t>90291167</t>
+  </si>
+  <si>
+    <t>17138418</t>
+  </si>
+  <si>
+    <t>30181956</t>
+  </si>
+  <si>
+    <t>23620619</t>
+  </si>
+  <si>
+    <t>600000</t>
+  </si>
+  <si>
+    <t>130639222</t>
+  </si>
+  <si>
+    <t>128939222</t>
+  </si>
+  <si>
+    <t>28328656</t>
+  </si>
+  <si>
+    <t>111798613</t>
+  </si>
+  <si>
+    <t>2277844</t>
+  </si>
+  <si>
+    <t>141186422</t>
+  </si>
+  <si>
+    <t>9622007</t>
+  </si>
+  <si>
+    <t>7065617</t>
+  </si>
+  <si>
+    <t>5883198</t>
+  </si>
+  <si>
+    <t>94017261</t>
+  </si>
+  <si>
+    <t>Obras y Servicios Públicos consolidados. Sin montos específicos para Salud o Cultura en clasificación funcional.</t>
+  </si>
+  <si>
+    <t>247423181</t>
+  </si>
+  <si>
+    <t>97818494</t>
+  </si>
+  <si>
+    <t>4676192</t>
+  </si>
+  <si>
+    <t>26985491</t>
+  </si>
+  <si>
+    <t>14751408</t>
+  </si>
+  <si>
+    <t>1493577</t>
+  </si>
+  <si>
+    <t>101698019</t>
+  </si>
+  <si>
+    <t>93507990</t>
+  </si>
+  <si>
+    <t>23755780</t>
+  </si>
+  <si>
+    <t>104761772</t>
+  </si>
+  <si>
+    <t>1524681</t>
+  </si>
+  <si>
+    <t>19587507</t>
+  </si>
+  <si>
+    <t>10177316</t>
+  </si>
+  <si>
+    <t>3249764</t>
+  </si>
+  <si>
+    <t>8663919</t>
+  </si>
+  <si>
+    <t>5717941</t>
+  </si>
+  <si>
+    <t>88292469</t>
+  </si>
+  <si>
+    <t>Sin recursos para comunicación social ni pago de pensiones y jubilaciones.</t>
+  </si>
+  <si>
+    <t>Documento preliminar sin desgloses numéricos en los fragmentos disponibles.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1902,43 +3172,577 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="29">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D6564C61-54B6-4147-8CE5-2F11C4DE4F8D}" name="Tabla1" displayName="Tabla1" ref="A1:AA56" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
+  <autoFilter ref="A1:AA56" xr:uid="{D6564C61-54B6-4147-8CE5-2F11C4DE4F8D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA56">
+    <sortCondition ref="A1:A56"/>
+  </sortState>
+  <tableColumns count="27">
+    <tableColumn id="1" xr3:uid="{E389947C-DD6B-4F6F-A981-A8C84102425D}" name="Municipio" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{D29E3496-7D0A-46DC-A174-ABD41C3F81A7}" name="Año" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{02FCD76F-A997-4E0B-9271-96AF7096D258}" name="Presupuesto_Total" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{3EF0D8E2-1FFE-4D1D-AA04-B321609D2BDE}" name="Cap1000" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{22289C70-F297-4CC5-9618-81E2DD111C74}" name="Cap2000" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{AB876155-3943-4914-9BAB-CFBCFBDBEF41}" name="Cap3000" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{1B6809B1-D21C-41B0-A478-096D94C34620}" name="Cap4000" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{216E49CB-D188-4FDF-BC44-F78EA7F024E2}" name="Cap5000" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{E7B20B40-F369-423D-A49A-93E6958A1794}" name="Cap6000" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{99814B48-8610-42CD-AB9F-1DE409368347}" name="Cap9000" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{0A0C5EFC-840A-405E-8EFF-86D1F5A8E841}" name="FAISM" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{98072D78-5FE1-42CA-9B25-E69A4EC9E7D8}" name="FORTAMUN" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{F5E0BD87-9503-46FC-9229-39A32870B53B}" name="Participaciones_Fed" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{80D73DF9-2ECE-4D06-B080-192523A30A10}" name="PC_Dir" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{9075A48F-9248-4B1C-98C6-DB3F0E83DB3C}" name="ObrasPublicas_Dir" dataDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{5827790F-4F6D-4D2C-A35C-1F59959F7180}" name="AguaPotable_Dir" dataDxfId="11"/>
+    <tableColumn id="17" xr3:uid="{FE4A3ED9-EEBE-4EF5-8007-41911ED5589C}" name="ServiciosPublicos_Dir" dataDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{EAD8E391-0DF2-4B21-AB68-3E189137A2C7}" name="DesarrolloRural_Dir" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{A6369E57-EFB8-4B34-AFF1-F1F0611C2FBA}" name="EducacionCultura_Dir" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{9DA379F4-8EC9-4A98-9192-F9E571A8BD65}" name="DIF_Transfer" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{CBC72F52-9C93-4B8A-8C95-C8ACB3EDF399}" name="FC_ProteccionCivil" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{5DCF9302-D3BD-4FD8-9328-079A11A6A023}" name="FC_Vivienda_Servicios" dataDxfId="5"/>
+    <tableColumn id="23" xr3:uid="{EFB570A8-8B45-4060-B970-EBFD0900BF96}" name="FC_ProteccionAmbiental" dataDxfId="4"/>
+    <tableColumn id="24" xr3:uid="{7963CCBA-8DCA-4D0C-9268-980C2906381F}" name="FC_Salud" dataDxfId="3"/>
+    <tableColumn id="25" xr3:uid="{BCEA62B3-9460-4700-AE36-A64AA919C9FF}" name="FC_Cultura" dataDxfId="2"/>
+    <tableColumn id="26" xr3:uid="{E242E916-CD83-42A9-91AE-6A2B8A88E177}" name="Observaciones" dataDxfId="1"/>
+    <tableColumn id="27" xr3:uid="{F765BC89-A5BD-4932-8687-811F98CA5209}" name="Fuente" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2128,17 +3932,35 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AA56"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="19.08984375" customWidth="1"/>
+    <col min="12" max="12" width="13.08984375" customWidth="1"/>
+    <col min="13" max="13" width="20.1796875" customWidth="1"/>
+    <col min="15" max="15" width="18.81640625" customWidth="1"/>
+    <col min="16" max="16" width="17.08984375" customWidth="1"/>
+    <col min="17" max="17" width="21.54296875" customWidth="1"/>
+    <col min="18" max="18" width="19.6328125" customWidth="1"/>
+    <col min="19" max="19" width="21.54296875" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="19.08984375" customWidth="1"/>
+    <col min="22" max="22" width="22.36328125" customWidth="1"/>
+    <col min="23" max="23" width="23.90625" customWidth="1"/>
+    <col min="26" max="26" width="15.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2221,2675 +4043,4589 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>985</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA2" s="1" t="s">
+      <c r="C5" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="S5" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>366</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>69</v>
+      <c r="C6" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>89</v>
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>402</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA6" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>111</v>
+        <v>891</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>150</v>
+        <v>946</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>151</v>
+        <v>947</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>152</v>
+        <v>948</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>153</v>
+        <v>949</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>154</v>
+        <v>950</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>155</v>
+        <v>951</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>156</v>
+        <v>952</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>157</v>
+        <v>910</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>158</v>
+        <v>953</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>159</v>
+        <v>954</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>160</v>
+        <v>955</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>161</v>
+        <v>956</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>162</v>
+        <v>957</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>163</v>
+        <v>958</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>44</v>
+        <v>959</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>960</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>165</v>
+        <v>961</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>156</v>
+        <v>962</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>108</v>
+        <v>963</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>167</v>
+        <v>964</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>168</v>
+        <v>409</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>111</v>
+        <v>891</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>169</v>
+        <v>965</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>170</v>
+        <v>966</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>171</v>
+        <v>967</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>172</v>
+        <v>968</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>173</v>
+        <v>969</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>174</v>
+        <v>970</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>175</v>
+        <v>971</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>176</v>
+        <v>338</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>177</v>
+        <v>972</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>178</v>
+        <v>973</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>179</v>
+        <v>974</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>180</v>
+        <v>975</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>181</v>
+        <v>976</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>182</v>
+        <v>977</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>44</v>
+        <v>978</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>979</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>184</v>
+        <v>980</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>175</v>
+        <v>981</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X9" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y9" s="2" t="s">
-        <v>108</v>
+        <v>982</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>187</v>
+        <v>983</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>984</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>188</v>
+        <v>622</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>189</v>
+        <v>623</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>190</v>
+        <v>624</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>191</v>
+        <v>625</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>192</v>
+        <v>626</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>193</v>
+        <v>627</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>194</v>
+        <v>628</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>195</v>
+        <v>629</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>196</v>
+        <v>584</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>197</v>
+        <v>630</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>198</v>
+        <v>631</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>199</v>
+        <v>632</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>200</v>
+        <v>633</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>201</v>
+        <v>634</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>202</v>
+        <v>635</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>204</v>
+        <v>635</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>205</v>
+        <v>636</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>206</v>
+        <v>637</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>108</v>
+        <v>633</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>207</v>
+        <v>638</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>208</v>
+        <v>639</v>
       </c>
       <c r="X10" s="2" t="s">
         <v>108</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>108</v>
+        <v>640</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>209</v>
+        <v>641</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>210</v>
+        <v>584</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>188</v>
+        <v>622</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>50</v>
+        <v>231</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>211</v>
+        <v>642</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>212</v>
+        <v>643</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>213</v>
+        <v>644</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>214</v>
+        <v>645</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>215</v>
+        <v>646</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>216</v>
+        <v>647</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>217</v>
+        <v>648</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>218</v>
+        <v>649</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>219</v>
+        <v>650</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>220</v>
+        <v>651</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>44</v>
+        <v>652</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>653</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>222</v>
+        <v>654</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>223</v>
+        <v>655</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>224</v>
+        <v>656</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>225</v>
+        <v>657</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>226</v>
+        <v>658</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>206</v>
+        <v>659</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>108</v>
+        <v>653</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>227</v>
+        <v>660</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>228</v>
+        <v>661</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>108</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>108</v>
+        <v>658</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>229</v>
+        <v>662</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>230</v>
+        <v>586</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>188</v>
+        <v>622</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>231</v>
+        <v>70</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>232</v>
+        <v>663</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>233</v>
+        <v>643</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>234</v>
+        <v>664</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>235</v>
+        <v>665</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>236</v>
+        <v>666</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>237</v>
+        <v>667</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>238</v>
+        <v>668</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>239</v>
+        <v>669</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>240</v>
+        <v>670</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>241</v>
+        <v>671</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>242</v>
+        <v>672</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>243</v>
+        <v>673</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>244</v>
+        <v>674</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>245</v>
+        <v>675</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>246</v>
+        <v>676</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>247</v>
+        <v>677</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>248</v>
+        <v>678</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>249</v>
+        <v>679</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>108</v>
+        <v>673</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>250</v>
+        <v>680</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>251</v>
+        <v>681</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>108</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>108</v>
+        <v>682</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA12" s="2" t="s">
-        <v>253</v>
+        <v>683</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>188</v>
+        <v>622</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>254</v>
+        <v>684</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>255</v>
+        <v>685</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>256</v>
+        <v>686</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>257</v>
+        <v>687</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>258</v>
+        <v>688</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>259</v>
+        <v>689</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>260</v>
+        <v>690</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>261</v>
+        <v>691</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>262</v>
+        <v>692</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>263</v>
+        <v>693</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>264</v>
+        <v>694</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>265</v>
+        <v>695</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>266</v>
+        <v>696</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>267</v>
+        <v>697</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>268</v>
+        <v>698</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>269</v>
+        <v>699</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>270</v>
+        <v>700</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>249</v>
+        <v>701</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>108</v>
+        <v>695</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>271</v>
+        <v>702</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>272</v>
+        <v>703</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>273</v>
+        <v>108</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>274</v>
+        <v>700</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>275</v>
+        <v>704</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>276</v>
+        <v>89</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>277</v>
+        <v>622</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>291</v>
+      <c r="C14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y14" s="2" t="s">
-        <v>292</v>
+        <v>49</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>295</v>
+        <v>1041</v>
       </c>
       <c r="AA14" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="AA15" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="AA16" s="2" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B15" s="2" t="s">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="U15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="W15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z15" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="AA15" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="AA17" s="2" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B16" s="2" t="s">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="U16" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y16" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z16" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="AA16" s="2" t="s">
+      <c r="C18" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="AA18" s="2" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B17" s="2" t="s">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="W17" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X17" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y17" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z17" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="AA17" s="2" t="s">
+      <c r="C19" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X19" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="AA19" s="2" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B18" s="2" t="s">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X18" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="Y18" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z18" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="AA18" s="2" t="s">
-        <v>366</v>
+      <c r="C20" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA20" s="2" t="s">
+        <v>589</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B19" s="2" t="s">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="W19" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X19" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y19" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="Z19" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="AA19" s="2" t="s">
-        <v>383</v>
+      <c r="C21" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="AA21" s="2" t="s">
+        <v>740</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B20" s="2" t="s">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="U20" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="W20" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X20" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y20" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="Z20" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="AA20" s="2" t="s">
-        <v>402</v>
+      <c r="C22" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="AA22" s="2" t="s">
+        <v>757</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B21" s="2" t="s">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="U21" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="W21" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X21" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y21" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="Z21" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="AA21" s="2" t="s">
-        <v>409</v>
+      <c r="C23" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="AA23" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B22" s="2" t="s">
+    <row r="24" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="W22" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="X22" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="Y22" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="Z22" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="AA22" s="2" t="s">
-        <v>428</v>
+      <c r="C24" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="AA24" s="2" t="s">
+        <v>795</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="B23" s="2" t="s">
+    <row r="25" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="U23" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="W23" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X23" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y23" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z23" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="AA23" s="2" t="s">
-        <v>447</v>
+      <c r="C25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA25" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="B24" s="2" t="s">
+    <row r="26" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="T24" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="U24" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="W24" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X24" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y24" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z24" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="AA24" s="2" t="s">
-        <v>464</v>
+      <c r="C26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA26" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="U25" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="W25" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="X25" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y25" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="Z25" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="AA25" s="2" t="s">
-        <v>483</v>
+    <row r="27" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA27" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="B26" s="2" t="s">
+    <row r="28" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="W26" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X26" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y26" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="Z26" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="AA26" s="2" t="s">
-        <v>504</v>
+      <c r="C28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X28" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y28" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA28" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="B27" s="2" t="s">
+    <row r="29" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S27" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="T27" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="U27" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="V27" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="W27" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="X27" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y27" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z27" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="AA27" s="1" t="s">
+      <c r="C29" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="U29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z29" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA29" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="W30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z30" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA30" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="T28" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="U28" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="V28" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="W28" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X28" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y28" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z28" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="AA28" s="1" t="s">
-        <v>49</v>
+    <row r="31" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="U31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="W31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z31" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA31" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S29" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="T29" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="U29" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="V29" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="W29" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X29" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y29" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z29" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="AA29" s="2" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="S30" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="U30" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="V30" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="W30" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="X30" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y30" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z30" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="AA30" s="2" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="U31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="V31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="X31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z31" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="AA31" s="2" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="32">
+    <row r="32" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="T32" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="U32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z32" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA32" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="V32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="X32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z32" s="1" t="s">
+      <c r="C33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="AA32" s="2" t="s">
+      <c r="AA33" s="2" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="s">
+    <row r="34" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X34" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y34" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z34" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="AA34" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X35" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y35" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z35" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="AA35" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="T36" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="U36" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="W36" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X36" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y36" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z36" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="AA36" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="T37" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="W37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z37" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA37" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z38" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA38" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="T39" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="U39" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V39" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="W39" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="X39" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y39" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z39" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="AA39" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="T40" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="U40" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="W40" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="X40" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y40" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z40" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="AA40" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="S41" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="T41" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="U41" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="W41" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="X41" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y41" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="Z41" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="AA41" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="U42" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X42" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y42" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z42" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="AA42" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="T43" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="U43" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="W43" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X43" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y43" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="Z43" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="AA43" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="R44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="U44" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X44" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y44" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="Z44" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="AA44" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q45" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S45" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="T45" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="U45" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="V45" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="W45" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X45" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y45" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="Z45" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="AA45" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="R46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="U46" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="W46" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="X46" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="Y46" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="Z46" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="AA46" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="T47" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="U47" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V47" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="W47" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="X47" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y47" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z47" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="AA47" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q48" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R48" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="T48" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="U48" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V48" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="W48" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X48" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y48" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z48" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="AA48" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="R49" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="T49" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="U49" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="V49" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="W49" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X49" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y49" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z49" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="AA49" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q50" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="S50" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="T50" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="U50" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="W50" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X50" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y50" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z50" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="AA50" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="T51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="V51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z51" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="AA51" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="R52" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="T52" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="U52" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X52" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y52" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z52" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="AA52" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q53" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S53" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="T53" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="U53" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V53" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="W53" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X53" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y53" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z53" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="AA53" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="R54" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="S54" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="T54" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="U54" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="W54" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="X54" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y54" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="Z54" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="AA54" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="T55" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="U55" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="W55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y55" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="Z55" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="AA55" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="V33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="X33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z33" s="1" t="s">
+      <c r="C56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="T56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="V56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z56" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="AA33" s="2" t="s">
+      <c r="AA56" s="2" t="s">
         <v>581</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>582</v>
       </c>
@@ -4897,7 +8633,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>584</v>
       </c>
@@ -4905,7 +8641,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>586</v>
       </c>
@@ -4913,7 +8649,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>89</v>
       </c>
@@ -4921,7 +8657,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>589</v>
       </c>
@@ -4929,7 +8665,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>187</v>
       </c>
@@ -4937,7 +8673,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>131</v>
       </c>
@@ -4945,7 +8681,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>593</v>
       </c>
@@ -4953,7 +8689,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>595</v>
       </c>
@@ -4961,7 +8697,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>210</v>
       </c>
@@ -4969,7 +8705,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>230</v>
       </c>
@@ -4977,7 +8713,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>253</v>
       </c>
@@ -4985,7 +8721,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>600</v>
       </c>
@@ -4993,7 +8729,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>602</v>
       </c>
@@ -5001,7 +8737,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>296</v>
       </c>
@@ -5009,7 +8745,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>314</v>
       </c>
@@ -5017,7 +8753,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>330</v>
       </c>
@@ -5025,7 +8761,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>347</v>
       </c>
@@ -5033,7 +8769,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>366</v>
       </c>
@@ -5041,7 +8777,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>383</v>
       </c>
@@ -5049,7 +8785,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>402</v>
       </c>
@@ -5057,7 +8793,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>409</v>
       </c>
@@ -5065,7 +8801,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>428</v>
       </c>
@@ -5073,7 +8809,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>447</v>
       </c>
@@ -5081,7 +8817,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>464</v>
       </c>
@@ -5089,7 +8825,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>483</v>
       </c>
@@ -5097,7 +8833,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>504</v>
       </c>
@@ -5105,7 +8841,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>555</v>
       </c>
@@ -5113,7 +8849,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>571</v>
       </c>
@@ -5121,7 +8857,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>577</v>
       </c>
@@ -5129,7 +8865,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>579</v>
       </c>
@@ -5137,7 +8873,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>581</v>
       </c>
@@ -5146,6 +8882,6 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>